--- a/data/seed/portfolio/L-2024-9067/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-9067/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,33 +558,33 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>2214000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>47661000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6379 01.07.2026 QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9512</t>
         </is>
       </c>
     </row>
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>2203000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>6248000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
+          <t>Предоплата за маериалы по дог. №75/26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>1529000</v>
+        <v>1502000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Guliston Tikuv MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>235062338</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000727626431001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9186 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5701 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -681,40 +681,40 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>3676000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>3552000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №145/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2580</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,33 +722,33 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>2759000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>3137000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>394698237</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000366214219001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7352</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7547 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>12181000</v>
+        <v>1804000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №229/26, НДС 12%</t>
+          <t>Оплата по с/ф №3378 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -804,33 +804,33 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>3894000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>4207000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3766 06.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №239/26</t>
         </is>
       </c>
     </row>
@@ -846,39 +846,34 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1426000</v>
+        <v>8273000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Farg'ona Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>395023972</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000040126317001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №87/26, QQS bilan</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -886,23 +881,23 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>1848000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>3054000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -912,14 +907,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8110</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8176 07.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,40 +922,40 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>2203000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>1143000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovalar uchun to'lov h/f №5453</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3680</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,23 +963,23 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>3423000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>3666000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -994,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №36/26</t>
+          <t>Предоплата за товар по дог. №88/26 от 08.07.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1009,35 +1004,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>8273000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>3515000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Farg'ona Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №105/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1046,39 +1046,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>16753000</v>
+        <v>1112000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>287061898</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000789358122001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1086,40 +1086,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>28781000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>31080000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №291/26</t>
+          <t>Tovar uchun to'lov, h/f №5161 09.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,33 +1127,33 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>1112000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>1348000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish Materiallari XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>365106400</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000104308240001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Оплата за товар по счет-фактуре №6929 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>13513000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2636 09.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №22/26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,31 +1211,31 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>1749000</v>
+        <v>3642000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>323350623</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3886</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9082 10.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1250,33 +1250,33 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>1530000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>4250000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov,shartn. №185/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №216/26 от 10.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1292,32 +1292,32 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1346000</v>
+        <v>7943000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>394698237</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000366214219001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №284/26</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №238/26, QQS BILAN</t>
         </is>
       </c>
     </row>
@@ -1334,31 +1334,31 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>12454000</v>
+        <v>19726000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Farovon Mebel MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>389348383</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000203822845001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №235/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>11322000</v>
+        <v>2620000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SHARTNOMA №2/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1416,31 +1416,31 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>1032000</v>
+        <v>1314000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shodlik Agro Servis XK</t>
+          <t>Nukus Plastik AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>254416715</t>
+          <t>398888857</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000577845990001</t>
+          <t>20208000440484000001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №413</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №7061 13.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
@@ -1455,33 +1455,33 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>2869000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>1252000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №40/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4324 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1497,32 +1497,32 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3173000</v>
+        <v>5512000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro XK</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>328671904</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000609014365001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №159/26</t>
+          <t>Оплата за товары согласно счет-фактуре №6021</t>
         </is>
       </c>
     </row>
@@ -1538,32 +1538,32 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1121000</v>
+        <v>2158000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro XK</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>328671904</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000609014365001</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №88/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №2486</t>
         </is>
       </c>
     </row>
@@ -1580,21 +1580,21 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>2608000</v>
+        <v>3574000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4546 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1621,38 +1621,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>1492000</v>
+        <v>1714000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Nukus Plastik AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>398888857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>20208000440484000001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SHARTNOMA №250/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,33 +1660,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>1128000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>1254000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №72/26 от 15.07.2026</t>
         </is>
       </c>
     </row>
@@ -1727,14 +1727,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,40 +1742,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>2503000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>1128000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5024 за поставленный товар</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1783,40 +1783,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>7272000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>2584000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5570 20.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №3092</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1826,38 +1826,38 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>2500000</v>
+        <v>5153000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №23/26 bo'yicha oldindan tolov</t>
+          <t>Оплата по счет-фактуре №7855 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1865,33 +1865,33 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>1493000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>14421000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9172</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №137/26</t>
         </is>
       </c>
     </row>
@@ -1907,39 +1907,34 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>2449000</v>
+        <v>22700000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>238706189</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>16307000396907050417</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №18/26 от 0.07.2026, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1947,35 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>22700000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>4680000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
+          <t>Farg'ona Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>16307000396907050417</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по с/ф №4692 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>31617000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>1883000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>394698237</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000366214219001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №41/26</t>
+          <t>Предоплата за товар по дог. №3/26 от 22.07.2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>1178000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>1851000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tovar uchun tolov, hisob-faktura №2114 21.07.2026, QQS bilan</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1790000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>20748000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Guliston Tikuv MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>235062338</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000727626431001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата за продукцию по договору №4/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2107,39 +2107,39 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>2605000</v>
+        <v>5429000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №157/26</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6544</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>3457000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>1134000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №1/26</t>
+          <t>Предоплата за товар по договору №251/26 от 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>15344000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>695000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000479946982001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1762</t>
+          <t>Оплат за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2231,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>1184000</v>
+        <v>18358000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №204/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №4325 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>3723000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>3953000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Nukus Plastik AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>398888857</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000440484000001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №169/26</t>
+          <t>Tovar uchun to'lov, h/f №3253 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>4688000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>5176000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>4616000</v>
+        <v>5225000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>2858000</v>
+        <v>1208000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Shartnoma №263/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8192 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,38 +2436,38 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>2450000</v>
+        <v>3343000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №166/26 bo'yicha oldindan to'lov</t>
+          <t>SHARTNOMA №5/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,38 +2477,38 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>1134000</v>
+        <v>1196000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6181 27.07.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №988 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,23 +2516,23 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>695000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>2007000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000603284714001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,14 +2542,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2745</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2557,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>8491000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>6218000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Qarshi Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>241671545</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000784599081001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Shartnoma №266/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №6720</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2598,35 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>1289000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>389683164</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №152/26, НДС 12%</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2640,39 +2635,39 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>9214000</v>
+        <v>2228000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №5/26, QQS bilan</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №186/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2682,38 +2677,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>13606000</v>
+        <v>12312000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Nukus Plastik AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>398888857</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000440484000001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9980 29.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8524 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2718,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>3433000</v>
+        <v>8994000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Guliston Tikuv MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>235062338</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000727626431001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9613 29.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №113/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2764,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>1982000</v>
+        <v>4516000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7232</t>
+          <t>Предоплата за товар по договору №155/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2803,40 +2798,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>1268000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>1970000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>394698237</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000366214219001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №49/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5682 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2844,40 +2839,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>1757000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>804000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8810</t>
+          <t>Оплата за упаковочные материалы, с/ф №7765</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2886,27 +2881,32 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>300000</v>
+        <v>1992000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за упаковочные материалы, с/ф №7770</t>
         </is>
       </c>
     </row>
@@ -2921,40 +2921,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>8142000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №252/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №8/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2962,40 +2962,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>3782000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>1202000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №76/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №244/26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>1911000</v>
+        <v>4849000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Shartnoma №207/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №91/26 от 06.08.2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3044,40 +3044,35 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>1542000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>8898000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>389683164</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №525</t>
+          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА ИЮЛЬ 2026 Г. СОГЛАСНО РЕЕСТРУ №3594</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>11723000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>1927000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №14/26, QQS bilan</t>
+          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3127,22 +3122,22 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>24447000</v>
+        <v>2574000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>394698237</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000366214219001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №104/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №7/26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3169,38 +3164,38 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>1999000</v>
+        <v>17096000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №101/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4512</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,34 +3204,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>8898000</v>
+        <v>1196000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>287061898</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000789358122001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. ПО ДОГ. №7/20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3245,39 +3245,39 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>4378000</v>
+        <v>3208000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №87/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №145/26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3285,40 +3285,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>7493000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>1172000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4461 06.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №4181</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3326,40 +3326,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>8410000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>2197000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №84/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5702 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3367,40 +3367,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>4983000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>725000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SHARTNOMA №115/26 BO'YIHA OLDINDAN TO'LOV</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №262/26 ОТ 13.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3408,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>4348000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>895000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9941</t>
+          <t>Оплата за транспортные услуги по договору №68/26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3449,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>2417000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>18328000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1536 10.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №10/26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>2301000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>1213000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SHARTNOMA №25/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>IJTIMOIY SOLIQ IYUL 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3531,40 +3531,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>1579000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>1213000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №926 10.08.2026, QQS bilan</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3574,38 +3574,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>1496000</v>
+        <v>2747000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6145</t>
+          <t>Оплата за продукцию по дог. №242/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3614,22 +3614,22 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>1196000</v>
+        <v>698000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish Materiallari XK</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>365106400</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000104308240001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3639,14 +3639,14 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по дог. №80/22</t>
+          <t>Оплата за сырье по дог. №103/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3655,22 +3655,22 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>5912000</v>
+        <v>5257000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'ov h/f №302</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №173/26</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3697,38 +3697,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>13898000</v>
+        <v>8628000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bunyodkor Qurilish XK</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>286988888</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000794404840001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №248/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №8185 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3736,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>5033000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>1098000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №47/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3119</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3777,40 +3777,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>1979000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>1135000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №177/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №62/26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3818,40 +3818,35 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>20712000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>22700000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>389683164</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>16307000396907050417</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №88/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3859,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>6496000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №91/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №2152</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3900,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>42905000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Оплата за товар по счет-фактуре №5916 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3941,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>6988000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4133</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3982,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>7038000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>6390000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №205/26</t>
+          <t>Shartnoma №87/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4025,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>4062000</v>
+        <v>2162000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №262/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №230/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4064,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>3118000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>748000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000479946982001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8002</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4105,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>3074000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>1964000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>323350623</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №88/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4146,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>2358000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>74664000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №264/26 от 17.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №4817</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4187,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>16129000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>4014000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №23/26</t>
+          <t>Предоплата за товар по договору №291/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4228,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>5289000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>1448000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №255/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №22/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4269,40 +4264,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>2408000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>1944000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №2/26 от 19.08.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №6902</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4310,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>5029000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>2274000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №2571</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4351,35 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>22700000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>19689000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>16307000396907050417</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №2768 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4389,21 +4389,21 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>2140000</v>
+        <v>8431000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>323350623</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5428 24.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4733 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>1239000</v>
+        <v>5398000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8966</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8919 ОТ 28.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4470,39 +4470,39 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>1975000</v>
+        <v>1809000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Оплата за упаковочные материалы, с/ф №1854</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4510,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2457000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №278/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2532</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4551,35 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>4193000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>389683164</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Shartnoma №228/26 bo'yicha oldindan to'lov</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4589,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>1978000</v>
+        <v>4553000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shodlik Agro Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>254416715</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000577845990001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №9544 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4634,39 +4629,39 @@
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>9538000</v>
+        <v>1943000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №140/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №216/26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4676,38 +4671,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>3618000</v>
+        <v>73222000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6861 27.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7108 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4716,39 +4711,39 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>748000</v>
+        <v>2845000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000603284714001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №236/26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4758,38 +4753,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>29084000</v>
+        <v>3360000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Guliston Tikuv MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>235062338</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000727626431001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №173/26 от 31.08.2026</t>
+          <t>Предоплата за товар по договору №142/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4799,21 +4794,21 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>4758000</v>
+        <v>2627000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>323350623</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,14 +4818,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №119/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7916 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4833,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>2162000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>2754000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4292 31.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №1022</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4879,35 +4874,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>5467000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Farg'ona Yog'och XK</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Предоплата за товар по договору №184/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,40 +4915,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>11453000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>2259000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №25/26</t>
+          <t>Оплата за товар по счет-фактуре №4232 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4957,39 +4957,39 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>21826000</v>
+        <v>1161000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>287061898</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000789358122001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5981</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №7/20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4998,22 +4998,17 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>4995000</v>
+        <v>8640000</v>
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro XK</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>328671904</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000609014365001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5023,14 +5018,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №5867</t>
+          <t>ЗАРАБОТНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5038,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>3092000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>871000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jizzax Tur Servis MChJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>207438810</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000776200512001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4316</t>
+          <t>Оплата за транспортные услуги по дог. №159/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5079,40 +5074,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>12210000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>6889000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №225/26</t>
+          <t>Предоплата за товар по договору №23/26 от 14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5122,38 +5117,38 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>4340000</v>
+        <v>5596000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Sarbon Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>334838312</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000382284595001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1637</t>
+          <t>Оплата по с/ф №8350 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5163,38 +5158,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>4214000</v>
+        <v>2530000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №110/26 от 07.09.2026</t>
+          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5202,40 +5197,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>1355000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>811000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5930 за поставленный товар</t>
+          <t>Оплата за сырье по договору №214/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5243,40 +5238,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>1086000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>4658000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Toshkent Poligraf XK</t>
+          <t>Zafar Plastik MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>308922020</t>
+          <t>343881017</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000573981104001</t>
+          <t>20208000620051254001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №204/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5285,34 +5280,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>8640000</v>
+        <v>10889000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №6414</t>
+          <t>Tovarlar uchun to'lov h/f №2351</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5322,38 +5322,38 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>10148000</v>
+        <v>11668000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №13/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №117/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5363,38 +5363,38 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>1855000</v>
+        <v>2090000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №212/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №37/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5403,39 +5403,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>1161000</v>
+        <v>1178000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>365106400</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000104308240001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5444,39 +5444,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>4154000</v>
+        <v>1178000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2107</t>
+          <t>НДФЛ ЗА АВГУСТ 2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5485,39 +5485,39 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>15884000</v>
+        <v>2436000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6037</t>
+          <t>Предоплата за материалы по договору №71/26</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5525,40 +5525,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>812000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>3318000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №148/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по дог. №157/26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5566,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>756000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>18091000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9954</t>
+          <t>Предоплата за материалы по договору №236/26</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5609,38 +5609,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>3887000</v>
+        <v>7700000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Bunyodkor Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>380812310</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000429242309001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7601 11.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №45/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>3670000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>323350623</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9746 11.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №6243</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,40 +5689,35 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>1810000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>22700000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bekobod Mebel XK</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>323350623</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000867276264001</t>
+          <t>16307000396907050417</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1117 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5730,40 +5725,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>19143000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>1204000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1936 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №258/26</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5771,23 +5766,23 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>2120000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>2275000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Farovon Mebel MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>389348383</t>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000203822845001</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5797,14 +5792,14 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7042 14.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №232/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5813,22 +5808,22 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>2833000</v>
+        <v>63321000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bunyodkor Sut MChJ</t>
+          <t>Nurafshon Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>207287058</t>
+          <t>320702615</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000188063179001</t>
+          <t>20208000670733898001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5838,14 +5833,14 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №100/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №131/26</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5855,38 +5850,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>1715000</v>
+        <v>6182000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8626 16.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог.№254/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5896,21 +5891,21 @@
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1581000</v>
+        <v>2823000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5920,14 +5915,14 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4899 за поставленный товар</t>
+          <t>Оплата по с/ф №1006 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5936,39 +5931,39 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>1178000</v>
+        <v>1841000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>241671545</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000784599081001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА АВГУСТ 2026 Г.</t>
+          <t>Предоплата за материалы по дог. №133/26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5977,7 +5972,7 @@
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1178000</v>
+        <v>1940000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
@@ -6002,14 +5997,14 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6019,21 +6014,21 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>2651000</v>
+        <v>6700000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6043,14 +6038,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6247</t>
+          <t>Предоплата за товар по договору №140/26 от 24.09.2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6058,40 +6053,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>2848000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>726000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>228808123</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000074292423001</t>
+          <t>20208000479946982001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №202/26 от 18.09.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6100,22 +6095,22 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>11956000</v>
+        <v>1696000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
+          <t>Jizzax Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>238706189</t>
+          <t>392202035</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>20208000398110401001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6125,14 +6120,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1070</t>
+          <t>Предоплата за материалы по договору №163/26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6141,34 +6136,39 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>22700000</v>
+        <v>4522000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9067)</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>368409201</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>16307000396907050417</t>
+          <t>20208000347837797001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9067 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №9/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6178,38 +6178,38 @@
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>9047000</v>
+        <v>3584000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7312 21.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6219,38 +6219,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>1086000</v>
+        <v>10419000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kamalak Tekstil MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>389683164</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000135188120001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5585</t>
+          <t>Предоплата за товар по договору №25/26 от 30.09.2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6260,38 +6260,38 @@
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>1035000</v>
+        <v>4014000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bunyodkor Qog'oz MChJ</t>
+          <t>Farg'ona Yog'och XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>206207026</t>
+          <t>368316451</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000546707338001</t>
+          <t>20208000518812064001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8161 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6172 от 30.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6300,545 +6300,53 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>9604000</v>
+        <v>300000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Angren Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>238706189</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000578935812001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5074</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>54649000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Angren Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>238706189</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000578935812001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №14/26</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>486086000</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>479586000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>1953000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>1145000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>228808123</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000074292423001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №3672 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>59015000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Farovon Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>389348383</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000203822845001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1100</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>1123000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Sharq Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>348684092</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000113478377001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3349 25.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>16859000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>228808123</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000074292423001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7292 28.09.2026, QQS BILAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>2567000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>389683164</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000135188120001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Shartnoma №290/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>726000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000603284714001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>7345000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Angren Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>238706189</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000578935812001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №90/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>2270000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>389683164</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000135188120001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7333 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>1498000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Kamalak Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>389683164</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000135188120001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2392 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Sarbon Moliya Bank</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="n">
-        <v>483024000</v>
-      </c>
-      <c r="D164" s="4" t="n">
-        <v>476524000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C165" s="4" t="n">
+      <c r="C153" s="4" t="n">
         <v>45400000</v>
       </c>
-      <c r="D165" s="4" t="n"/>
+      <c r="D153" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
